--- a/data/trans_bre/P16A11-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,0</t>
+          <t>-0,64; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,0</t>
+          <t>-1,08; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,3</t>
+          <t>-0,08; 2,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,34</t>
+          <t>-0,08; 1,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,89</t>
+          <t>-0,81; 1,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,17</t>
+          <t>-1,82; 0,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,64</t>
+          <t>-0,64; 1,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-64,84; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,05; 352,68</t>
+          <t>-59,87; 426,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,63</t>
+          <t>-0,34; 3,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,66</t>
+          <t>-3,65; 0,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,87</t>
+          <t>-2,83; 0,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,31</t>
+          <t>-3,69; 0,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 187,51</t>
+          <t>-12,26; 188,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 22,84</t>
+          <t>-61,24; 22,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,41; 39,15</t>
+          <t>-68,04; 45,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 21,28</t>
+          <t>-72,02; 11,33</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 1,48</t>
+          <t>-6,22; 1,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 5,52</t>
+          <t>-2,74; 5,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -0,31</t>
+          <t>-8,08; -0,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 8,26</t>
+          <t>-3,82; 9,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 13,37</t>
+          <t>-41,67; 16,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 58,53</t>
+          <t>-19,18; 51,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,53; -2,35</t>
+          <t>-50,81; -6,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 161,94</t>
+          <t>-25,82; 167,89</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 8,71</t>
+          <t>-5,05; 8,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 11,47</t>
+          <t>-2,85; 10,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 13,73</t>
+          <t>2,01; 13,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 1,56</t>
+          <t>-7,76; 1,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 32,65</t>
+          <t>-14,99; 29,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 36,61</t>
+          <t>-6,97; 34,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 70,36</t>
+          <t>8,43; 69,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 6,24</t>
+          <t>-24,61; 6,07</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 14,31</t>
+          <t>-0,6; 14,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 14,21</t>
+          <t>-2,51; 14,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 10,58</t>
+          <t>-4,39; 11,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 38,94</t>
+          <t>-4,28; 36,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 41,13</t>
+          <t>-1,04; 41,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 30,66</t>
+          <t>-4,63; 31,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 26,88</t>
+          <t>-9,69; 30,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 90,34</t>
+          <t>-8,91; 80,89</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 17,81</t>
+          <t>0,06; 18,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 13,48</t>
+          <t>-3,32; 13,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 10,33</t>
+          <t>-5,46; 10,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 12,54</t>
+          <t>1,18; 13,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 42,38</t>
+          <t>-0,66; 41,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 25,24</t>
+          <t>-5,21; 24,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 20,68</t>
+          <t>-9,23; 20,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 23,4</t>
+          <t>2,09; 24,88</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,65</t>
+          <t>2,25; 5,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,22</t>
+          <t>2,19; 6,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,68</t>
+          <t>1,14; 4,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 23,27</t>
+          <t>1,21; 21,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,1; 47,7</t>
+          <t>16,41; 48,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,74; 39,26</t>
+          <t>11,94; 38,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,09; 33,25</t>
+          <t>7,41; 33,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,5; 150,83</t>
+          <t>6,66; 131,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A11-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1123,95%</t>
+          <t>-19,39%</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,0</t>
+          <t>-0,75; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,76</t>
+          <t>-2,76; 1,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>103,63%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,43</t>
+          <t>-0,05; 1,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,8</t>
+          <t>-0,94; 1,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,23</t>
+          <t>-1,94; 0,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,53</t>
+          <t>-0,51; 1,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,84; —</t>
+          <t>-71,87; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,87; 426,49</t>
+          <t>-72,18; 435,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 159,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-42,17%</t>
+          <t>-43,94%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,41</t>
+          <t>-0,44; 3,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,68</t>
+          <t>-3,62; 0,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,88</t>
+          <t>-2,69; 1,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,13</t>
+          <t>-3,61; 0,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 188,75</t>
+          <t>-13,62; 191,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,24; 22,14</t>
+          <t>-60,2; 26,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 45,08</t>
+          <t>-62,8; 49,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,02; 11,33</t>
+          <t>-70,21; 13,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>-13,3%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 1,73</t>
+          <t>-6,55; 1,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,29</t>
+          <t>-1,98; 5,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; -0,71</t>
+          <t>-7,58; -0,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 9,12</t>
+          <t>-5,07; 1,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 16,77</t>
+          <t>-43,99; 18,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 51,32</t>
+          <t>-15,11; 60,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,81; -6,22</t>
+          <t>-49,67; -3,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 167,89</t>
+          <t>-31,6; 11,71</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-11,18%</t>
+          <t>-7,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 8,2</t>
+          <t>-4,34; 8,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 10,99</t>
+          <t>-2,33; 11,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 13,68</t>
+          <t>2,13; 13,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,46</t>
+          <t>-6,36; 2,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 29,85</t>
+          <t>-12,88; 32,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 34,9</t>
+          <t>-5,8; 37,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 69,49</t>
+          <t>8,14; 69,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 6,07</t>
+          <t>-20,78; 9,38</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,99</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>-1,61%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 14,27</t>
+          <t>-0,2; 14,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 14,5</t>
+          <t>-1,98; 14,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 11,25</t>
+          <t>-4,01; 10,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 36,95</t>
+          <t>-6,08; 4,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 41,44</t>
+          <t>-1,02; 43,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 31,55</t>
+          <t>-3,61; 31,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 30,25</t>
+          <t>-8,8; 27,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 80,89</t>
+          <t>-12,14; 10,52</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 18,28</t>
+          <t>-0,16; 18,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 13,21</t>
+          <t>-3,28; 13,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 10,27</t>
+          <t>-5,6; 10,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 13,28</t>
+          <t>1,55; 12,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 41,61</t>
+          <t>-0,38; 43,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 24,49</t>
+          <t>-4,99; 24,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 20,41</t>
+          <t>-9,71; 20,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 24,88</t>
+          <t>2,5; 23,53</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,83</t>
+          <t>2,31; 5,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,17</t>
+          <t>2,18; 6,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,7</t>
+          <t>1,03; 4,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 21,93</t>
+          <t>0,1; 3,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,41; 48,5</t>
+          <t>17,09; 48,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,94; 38,67</t>
+          <t>12,42; 39,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 33,89</t>
+          <t>6,48; 34,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 131,33</t>
+          <t>0,52; 19,23</t>
         </is>
       </c>
     </row>
